--- a/results/train/multiclass_AD_results.xlsx
+++ b/results/train/multiclass_AD_results.xlsx
@@ -566,73 +566,73 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.574</v>
+        <v>0.68153</v>
       </c>
       <c r="C2" t="n">
-        <v>0.525</v>
+        <v>0.59675</v>
       </c>
       <c r="D2" t="n">
-        <v>0.633</v>
+        <v>0.79439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.726</v>
+        <v>0.83915</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.72287</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.84</v>
+        <v>0.78904</v>
       </c>
       <c r="I2" t="n">
-        <v>0.724</v>
+        <v>0.65159</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.796</v>
+        <v>0.87207</v>
       </c>
       <c r="L2" t="n">
-        <v>0.661</v>
+        <v>0.77316</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.392</v>
+        <v>0.41331</v>
       </c>
       <c r="O2" t="n">
-        <v>0.249</v>
+        <v>0.26965</v>
       </c>
       <c r="P2" t="n">
-        <v>0.917</v>
+        <v>0.88462</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.217</v>
+        <v>0.19608</v>
       </c>
       <c r="R2" t="n">
-        <v>0.833</v>
+        <v>0.83333</v>
       </c>
       <c r="S2" t="n">
-        <v>0.125</v>
+        <v>0.11111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.241</v>
+        <v>0.35895</v>
       </c>
       <c r="U2" t="n">
-        <v>0.336</v>
+        <v>0.44672</v>
       </c>
       <c r="V2" t="n">
-        <v>0.188</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
-        <v>0.607</v>
+        <v>0.60732</v>
       </c>
       <c r="X2" t="n">
-        <v>0.615</v>
+        <v>0.61481</v>
       </c>
       <c r="Y2" t="n">
         <v>0.6</v>
@@ -645,73 +645,73 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.577</v>
+        <v>0.67831</v>
       </c>
       <c r="C3" t="n">
-        <v>0.519</v>
+        <v>0.59184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.65</v>
+        <v>0.79439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.666</v>
+        <v>0.80309</v>
       </c>
       <c r="F3" t="n">
-        <v>0.499</v>
+        <v>0.67097</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.898</v>
+        <v>0.8399</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.72399</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0.772</v>
+        <v>0.84507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.628</v>
+        <v>0.73171</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.375</v>
+        <v>0.41617</v>
       </c>
       <c r="O3" t="n">
-        <v>0.238</v>
+        <v>0.27594</v>
       </c>
       <c r="P3" t="n">
-        <v>0.889</v>
+        <v>0.84615</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.211</v>
+        <v>0.19048</v>
       </c>
       <c r="R3" t="n">
-        <v>0.667</v>
+        <v>0.66667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.125</v>
+        <v>0.11111</v>
       </c>
       <c r="T3" t="n">
-        <v>0.347</v>
+        <v>0.44116</v>
       </c>
       <c r="U3" t="n">
-        <v>0.39</v>
+        <v>0.49177</v>
       </c>
       <c r="V3" t="n">
-        <v>0.312</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0.608</v>
+        <v>0.60831</v>
       </c>
       <c r="X3" t="n">
-        <v>0.617</v>
+        <v>0.61686</v>
       </c>
       <c r="Y3" t="n">
         <v>0.6</v>
@@ -724,73 +724,73 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.589</v>
+        <v>0.67502</v>
       </c>
       <c r="C4" t="n">
-        <v>0.596</v>
+        <v>0.60905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.582</v>
+        <v>0.75701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.769</v>
+        <v>0.8271500000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.70524</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.821</v>
+        <v>0.76423</v>
       </c>
       <c r="I4" t="n">
-        <v>0.788</v>
+        <v>0.68948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.857</v>
+        <v>0.85714</v>
       </c>
       <c r="K4" t="n">
-        <v>0.85</v>
+        <v>0.83278</v>
       </c>
       <c r="L4" t="n">
-        <v>0.826</v>
+        <v>0.79445</v>
       </c>
       <c r="M4" t="n">
         <v>0.875</v>
       </c>
       <c r="N4" t="n">
-        <v>0.515</v>
+        <v>0.46362</v>
       </c>
       <c r="O4" t="n">
-        <v>0.358</v>
+        <v>0.31412</v>
       </c>
       <c r="P4" t="n">
-        <v>0.917</v>
+        <v>0.88462</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.125</v>
+        <v>0.11111</v>
       </c>
       <c r="T4" t="n">
-        <v>0.273</v>
+        <v>0.39993</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.5997</v>
       </c>
       <c r="V4" t="n">
-        <v>0.188</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0.531</v>
+        <v>0.53125</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.56667</v>
       </c>
       <c r="Y4" t="n">
         <v>0.5</v>
@@ -803,49 +803,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.529</v>
+        <v>0.64939</v>
       </c>
       <c r="C5" t="n">
-        <v>0.526</v>
+        <v>0.59165</v>
       </c>
       <c r="D5" t="n">
-        <v>0.532</v>
+        <v>0.71963</v>
       </c>
       <c r="E5" t="n">
-        <v>0.714</v>
+        <v>0.81443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.555</v>
+        <v>0.6869499999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.733</v>
+        <v>0.6779500000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.753</v>
+        <v>0.64512</v>
       </c>
       <c r="J5" t="n">
-        <v>0.714</v>
+        <v>0.71429</v>
       </c>
       <c r="K5" t="n">
-        <v>0.709</v>
+        <v>0.7412</v>
       </c>
       <c r="L5" t="n">
-        <v>0.628</v>
+        <v>0.68141</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.465</v>
+        <v>0.47429</v>
       </c>
       <c r="O5" t="n">
-        <v>0.315</v>
+        <v>0.32949</v>
       </c>
       <c r="P5" t="n">
-        <v>0.889</v>
+        <v>0.84615</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -857,19 +857,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.268</v>
+        <v>0.39224</v>
       </c>
       <c r="U5" t="n">
-        <v>0.472</v>
+        <v>0.56637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.188</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
-        <v>0.532</v>
+        <v>0.53226</v>
       </c>
       <c r="X5" t="n">
-        <v>0.569</v>
+        <v>0.56897</v>
       </c>
       <c r="Y5" t="n">
         <v>0.5</v>
@@ -1023,76 +1023,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.527</v>
+        <v>0.6485</v>
       </c>
       <c r="C2" t="n">
-        <v>0.525</v>
+        <v>0.59675</v>
       </c>
       <c r="D2" t="n">
-        <v>0.529</v>
+        <v>0.71008</v>
       </c>
       <c r="E2" t="n">
-        <v>0.713</v>
+        <v>0.82333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.72287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.951</v>
+        <v>0.95621</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.724</v>
+        <v>0.65159</v>
       </c>
       <c r="J2" t="n">
-        <v>0.931</v>
+        <v>0.93093</v>
       </c>
       <c r="K2" t="n">
-        <v>0.747</v>
+        <v>0.81385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.661</v>
+        <v>0.77316</v>
       </c>
       <c r="M2" t="n">
-        <v>0.859</v>
+        <v>0.85906</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.40637</v>
       </c>
       <c r="O2" t="n">
-        <v>0.249</v>
+        <v>0.26965</v>
       </c>
       <c r="P2" t="n">
-        <v>0.785</v>
+        <v>0.82434</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.138</v>
+        <v>0.12346</v>
       </c>
       <c r="R2" t="n">
-        <v>0.833</v>
+        <v>0.83333</v>
       </c>
       <c r="S2" t="n">
-        <v>0.075</v>
+        <v>0.06666999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.185</v>
+        <v>0.28004</v>
       </c>
       <c r="U2" t="n">
-        <v>0.336</v>
+        <v>0.44672</v>
       </c>
       <c r="V2" t="n">
-        <v>0.127</v>
+        <v>0.20395</v>
       </c>
       <c r="W2" t="n">
-        <v>0.478</v>
+        <v>0.4784</v>
       </c>
       <c r="X2" t="n">
-        <v>0.615</v>
+        <v>0.61481</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.392</v>
+        <v>0.39153</v>
       </c>
     </row>
     <row r="3">
@@ -1102,76 +1102,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.522</v>
+        <v>0.64147</v>
       </c>
       <c r="C3" t="n">
-        <v>0.519</v>
+        <v>0.59184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.526</v>
+        <v>0.70018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.656</v>
+        <v>0.78922</v>
       </c>
       <c r="F3" t="n">
-        <v>0.499</v>
+        <v>0.67097</v>
       </c>
       <c r="G3" t="n">
-        <v>0.956</v>
+        <v>0.95806</v>
       </c>
       <c r="H3" t="n">
-        <v>0.864</v>
+        <v>0.81049</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.72399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.92</v>
+        <v>0.9204599999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.724</v>
+        <v>0.78853</v>
       </c>
       <c r="L3" t="n">
-        <v>0.628</v>
+        <v>0.73171</v>
       </c>
       <c r="M3" t="n">
-        <v>0.855</v>
+        <v>0.85492</v>
       </c>
       <c r="N3" t="n">
-        <v>0.361</v>
+        <v>0.408</v>
       </c>
       <c r="O3" t="n">
-        <v>0.238</v>
+        <v>0.27594</v>
       </c>
       <c r="P3" t="n">
-        <v>0.751</v>
+        <v>0.78245</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.093</v>
+        <v>0.08333</v>
       </c>
       <c r="R3" t="n">
-        <v>0.667</v>
+        <v>0.66667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05</v>
+        <v>0.04444</v>
       </c>
       <c r="T3" t="n">
-        <v>0.231</v>
+        <v>0.31521</v>
       </c>
       <c r="U3" t="n">
-        <v>0.39</v>
+        <v>0.49177</v>
       </c>
       <c r="V3" t="n">
-        <v>0.164</v>
+        <v>0.23194</v>
       </c>
       <c r="W3" t="n">
-        <v>0.482</v>
+        <v>0.48165</v>
       </c>
       <c r="X3" t="n">
-        <v>0.617</v>
+        <v>0.61686</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.395</v>
+        <v>0.39506</v>
       </c>
     </row>
     <row r="4">
@@ -1181,76 +1181,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.549</v>
+        <v>0.6462</v>
       </c>
       <c r="C4" t="n">
-        <v>0.596</v>
+        <v>0.60905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.508</v>
+        <v>0.6881699999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.757</v>
+        <v>0.81313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.70524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.958</v>
+        <v>0.96</v>
       </c>
       <c r="H4" t="n">
-        <v>0.805</v>
+        <v>0.7503</v>
       </c>
       <c r="I4" t="n">
-        <v>0.788</v>
+        <v>0.68948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.823</v>
+        <v>0.82289</v>
       </c>
       <c r="K4" t="n">
-        <v>0.797</v>
+        <v>0.78167</v>
       </c>
       <c r="L4" t="n">
-        <v>0.826</v>
+        <v>0.79445</v>
       </c>
       <c r="M4" t="n">
-        <v>0.769</v>
+        <v>0.7693</v>
       </c>
       <c r="N4" t="n">
-        <v>0.476</v>
+        <v>0.45231</v>
       </c>
       <c r="O4" t="n">
-        <v>0.358</v>
+        <v>0.31412</v>
       </c>
       <c r="P4" t="n">
-        <v>0.712</v>
+        <v>0.80762</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.182</v>
+        <v>0.16327</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1</v>
+        <v>0.08889</v>
       </c>
       <c r="T4" t="n">
-        <v>0.147</v>
+        <v>0.22458</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.5997</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.13816</v>
       </c>
       <c r="W4" t="n">
-        <v>0.504</v>
+        <v>0.50448</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.56667</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.455</v>
+        <v>0.4546</v>
       </c>
     </row>
     <row r="5">
@@ -1260,49 +1260,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.494</v>
+        <v>0.62052</v>
       </c>
       <c r="C5" t="n">
-        <v>0.526</v>
+        <v>0.59165</v>
       </c>
       <c r="D5" t="n">
-        <v>0.466</v>
+        <v>0.65235</v>
       </c>
       <c r="E5" t="n">
-        <v>0.702</v>
+        <v>0.80017</v>
       </c>
       <c r="F5" t="n">
-        <v>0.555</v>
+        <v>0.6869499999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.956</v>
+        <v>0.95806</v>
       </c>
       <c r="H5" t="n">
-        <v>0.724</v>
+        <v>0.66986</v>
       </c>
       <c r="I5" t="n">
-        <v>0.753</v>
+        <v>0.64512</v>
       </c>
       <c r="J5" t="n">
-        <v>0.697</v>
+        <v>0.69656</v>
       </c>
       <c r="K5" t="n">
-        <v>0.663</v>
+        <v>0.69116</v>
       </c>
       <c r="L5" t="n">
-        <v>0.628</v>
+        <v>0.68141</v>
       </c>
       <c r="M5" t="n">
-        <v>0.701</v>
+        <v>0.70119</v>
       </c>
       <c r="N5" t="n">
-        <v>0.431</v>
+        <v>0.46088</v>
       </c>
       <c r="O5" t="n">
-        <v>0.315</v>
+        <v>0.32949</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.76656</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.146</v>
+        <v>0.22194</v>
       </c>
       <c r="U5" t="n">
-        <v>0.472</v>
+        <v>0.56637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.13801</v>
       </c>
       <c r="W5" t="n">
-        <v>0.509</v>
+        <v>0.50942</v>
       </c>
       <c r="X5" t="n">
-        <v>0.569</v>
+        <v>0.56897</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.461</v>
+        <v>0.46116</v>
       </c>
     </row>
   </sheetData>
@@ -1480,76 +1480,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.499</v>
+        <v>0.62446</v>
       </c>
       <c r="C2" t="n">
-        <v>0.525</v>
+        <v>0.59675</v>
       </c>
       <c r="D2" t="n">
-        <v>0.475</v>
+        <v>0.65487</v>
       </c>
       <c r="E2" t="n">
-        <v>0.701</v>
+        <v>0.81023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.72287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.91</v>
+        <v>0.92161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.781</v>
+        <v>0.73664</v>
       </c>
       <c r="I2" t="n">
-        <v>0.724</v>
+        <v>0.65159</v>
       </c>
       <c r="J2" t="n">
-        <v>0.847</v>
+        <v>0.84723</v>
       </c>
       <c r="K2" t="n">
-        <v>0.699</v>
+        <v>0.75651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.661</v>
+        <v>0.77316</v>
       </c>
       <c r="M2" t="n">
-        <v>0.741</v>
+        <v>0.74057</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.39889</v>
       </c>
       <c r="O2" t="n">
-        <v>0.249</v>
+        <v>0.26965</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76602</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05</v>
+        <v>0.04479</v>
       </c>
       <c r="R2" t="n">
-        <v>0.833</v>
+        <v>0.83333</v>
       </c>
       <c r="S2" t="n">
-        <v>0.026</v>
+        <v>0.02302</v>
       </c>
       <c r="T2" t="n">
-        <v>0.16</v>
+        <v>0.24457</v>
       </c>
       <c r="U2" t="n">
-        <v>0.336</v>
+        <v>0.44672</v>
       </c>
       <c r="V2" t="n">
-        <v>0.105</v>
+        <v>0.16838</v>
       </c>
       <c r="W2" t="n">
-        <v>0.466</v>
+        <v>0.4664</v>
       </c>
       <c r="X2" t="n">
-        <v>0.615</v>
+        <v>0.61481</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.376</v>
+        <v>0.37571</v>
       </c>
     </row>
     <row r="3">
@@ -1559,76 +1559,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.492</v>
+        <v>0.61298</v>
       </c>
       <c r="C3" t="n">
-        <v>0.519</v>
+        <v>0.59184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.468</v>
+        <v>0.63569</v>
       </c>
       <c r="E3" t="n">
-        <v>0.643</v>
+        <v>0.77183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.499</v>
+        <v>0.67097</v>
       </c>
       <c r="G3" t="n">
-        <v>0.903</v>
+        <v>0.90837</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.7716499999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.72399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.826</v>
+        <v>0.82604</v>
       </c>
       <c r="K3" t="n">
-        <v>0.669</v>
+        <v>0.72288</v>
       </c>
       <c r="L3" t="n">
-        <v>0.628</v>
+        <v>0.73171</v>
       </c>
       <c r="M3" t="n">
-        <v>0.714</v>
+        <v>0.7142500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.348</v>
+        <v>0.39873</v>
       </c>
       <c r="O3" t="n">
-        <v>0.238</v>
+        <v>0.27594</v>
       </c>
       <c r="P3" t="n">
-        <v>0.65</v>
+        <v>0.71838</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.014</v>
+        <v>0.01258</v>
       </c>
       <c r="R3" t="n">
-        <v>0.667</v>
+        <v>0.66667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007</v>
+        <v>0.00635</v>
       </c>
       <c r="T3" t="n">
-        <v>0.205</v>
+        <v>0.27594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.39</v>
+        <v>0.49177</v>
       </c>
       <c r="V3" t="n">
-        <v>0.139</v>
+        <v>0.19177</v>
       </c>
       <c r="W3" t="n">
-        <v>0.471</v>
+        <v>0.47129</v>
       </c>
       <c r="X3" t="n">
-        <v>0.617</v>
+        <v>0.61686</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.381</v>
+        <v>0.38131</v>
       </c>
     </row>
     <row r="4">
@@ -1638,76 +1638,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.528</v>
+        <v>0.62845</v>
       </c>
       <c r="C4" t="n">
-        <v>0.596</v>
+        <v>0.60905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.475</v>
+        <v>0.64912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.746</v>
+        <v>0.80267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.70524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926</v>
+        <v>0.93132</v>
       </c>
       <c r="H4" t="n">
-        <v>0.778</v>
+        <v>0.72643</v>
       </c>
       <c r="I4" t="n">
-        <v>0.788</v>
+        <v>0.68948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.768</v>
+        <v>0.76757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.757</v>
+        <v>0.7433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.826</v>
+        <v>0.79445</v>
       </c>
       <c r="M4" t="n">
-        <v>0.698</v>
+        <v>0.69834</v>
       </c>
       <c r="N4" t="n">
-        <v>0.466</v>
+        <v>0.44471</v>
       </c>
       <c r="O4" t="n">
-        <v>0.358</v>
+        <v>0.31412</v>
       </c>
       <c r="P4" t="n">
-        <v>0.669</v>
+        <v>0.76112</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.113</v>
+        <v>0.10127</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06</v>
+        <v>0.05333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.129</v>
+        <v>0.19807</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.5997</v>
       </c>
       <c r="V4" t="n">
-        <v>0.074</v>
+        <v>0.11863</v>
       </c>
       <c r="W4" t="n">
-        <v>0.498</v>
+        <v>0.49826</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.56667</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.445</v>
+        <v>0.4446</v>
       </c>
     </row>
     <row r="5">
@@ -1717,49 +1717,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.477</v>
+        <v>0.59984</v>
       </c>
       <c r="C5" t="n">
-        <v>0.526</v>
+        <v>0.59165</v>
       </c>
       <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.60826</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.555</v>
+        <v>0.6869499999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.903</v>
+        <v>0.90837</v>
       </c>
       <c r="H5" t="n">
-        <v>0.706</v>
+        <v>0.65447</v>
       </c>
       <c r="I5" t="n">
-        <v>0.753</v>
+        <v>0.64512</v>
       </c>
       <c r="J5" t="n">
-        <v>0.664</v>
+        <v>0.66409</v>
       </c>
       <c r="K5" t="n">
-        <v>0.624</v>
+        <v>0.64905</v>
       </c>
       <c r="L5" t="n">
-        <v>0.628</v>
+        <v>0.68141</v>
       </c>
       <c r="M5" t="n">
-        <v>0.62</v>
+        <v>0.6196199999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.42</v>
+        <v>0.4509</v>
       </c>
       <c r="O5" t="n">
-        <v>0.315</v>
+        <v>0.32949</v>
       </c>
       <c r="P5" t="n">
-        <v>0.631</v>
+        <v>0.714</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1771,22 +1771,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.125</v>
+        <v>0.1916</v>
       </c>
       <c r="U5" t="n">
-        <v>0.472</v>
+        <v>0.56637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1153</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.50013</v>
       </c>
       <c r="X5" t="n">
-        <v>0.569</v>
+        <v>0.56897</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.446</v>
+        <v>0.44616</v>
       </c>
     </row>
   </sheetData>
@@ -1937,76 +1937,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.493</v>
+        <v>0.61904</v>
       </c>
       <c r="C2" t="n">
-        <v>0.516</v>
+        <v>0.58849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.471</v>
+        <v>0.65293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.701</v>
+        <v>0.81023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.72287</v>
       </c>
       <c r="G2" t="n">
-        <v>0.91</v>
+        <v>0.92161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.781</v>
+        <v>0.73664</v>
       </c>
       <c r="I2" t="n">
-        <v>0.724</v>
+        <v>0.65159</v>
       </c>
       <c r="J2" t="n">
-        <v>0.847</v>
+        <v>0.84723</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.75264</v>
       </c>
       <c r="L2" t="n">
-        <v>0.651</v>
+        <v>0.76512</v>
       </c>
       <c r="M2" t="n">
-        <v>0.741</v>
+        <v>0.74057</v>
       </c>
       <c r="N2" t="n">
-        <v>0.325</v>
+        <v>0.36546</v>
       </c>
       <c r="O2" t="n">
-        <v>0.212</v>
+        <v>0.23997</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76602</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.833</v>
+        <v>0.83333</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.16</v>
+        <v>0.24457</v>
       </c>
       <c r="U2" t="n">
-        <v>0.336</v>
+        <v>0.44672</v>
       </c>
       <c r="V2" t="n">
-        <v>0.105</v>
+        <v>0.16838</v>
       </c>
       <c r="W2" t="n">
-        <v>0.466</v>
+        <v>0.4664</v>
       </c>
       <c r="X2" t="n">
-        <v>0.615</v>
+        <v>0.61481</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.376</v>
+        <v>0.37571</v>
       </c>
     </row>
     <row r="3">
@@ -2016,76 +2016,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.489</v>
+        <v>0.60969</v>
       </c>
       <c r="C3" t="n">
-        <v>0.511</v>
+        <v>0.58572</v>
       </c>
       <c r="D3" t="n">
-        <v>0.468</v>
+        <v>0.63569</v>
       </c>
       <c r="E3" t="n">
-        <v>0.643</v>
+        <v>0.77183</v>
       </c>
       <c r="F3" t="n">
-        <v>0.499</v>
+        <v>0.67097</v>
       </c>
       <c r="G3" t="n">
-        <v>0.903</v>
+        <v>0.90837</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.7716499999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.72399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.826</v>
+        <v>0.82604</v>
       </c>
       <c r="K3" t="n">
-        <v>0.665</v>
+        <v>0.71918</v>
       </c>
       <c r="L3" t="n">
-        <v>0.621</v>
+        <v>0.72418</v>
       </c>
       <c r="M3" t="n">
-        <v>0.714</v>
+        <v>0.7142500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.311</v>
+        <v>0.3733</v>
       </c>
       <c r="O3" t="n">
-        <v>0.205</v>
+        <v>0.25216</v>
       </c>
       <c r="P3" t="n">
-        <v>0.65</v>
+        <v>0.71838</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.014</v>
+        <v>0.01258</v>
       </c>
       <c r="R3" t="n">
-        <v>0.667</v>
+        <v>0.66667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007</v>
+        <v>0.00635</v>
       </c>
       <c r="T3" t="n">
-        <v>0.205</v>
+        <v>0.27594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.39</v>
+        <v>0.49177</v>
       </c>
       <c r="V3" t="n">
-        <v>0.139</v>
+        <v>0.19177</v>
       </c>
       <c r="W3" t="n">
-        <v>0.471</v>
+        <v>0.47129</v>
       </c>
       <c r="X3" t="n">
-        <v>0.617</v>
+        <v>0.61686</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.381</v>
+        <v>0.38131</v>
       </c>
     </row>
     <row r="4">
@@ -2095,76 +2095,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.524</v>
+        <v>0.62368</v>
       </c>
       <c r="C4" t="n">
-        <v>0.585</v>
+        <v>0.60016</v>
       </c>
       <c r="D4" t="n">
-        <v>0.475</v>
+        <v>0.64912</v>
       </c>
       <c r="E4" t="n">
-        <v>0.746</v>
+        <v>0.80267</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.70524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.926</v>
+        <v>0.93132</v>
       </c>
       <c r="H4" t="n">
-        <v>0.778</v>
+        <v>0.72643</v>
       </c>
       <c r="I4" t="n">
-        <v>0.788</v>
+        <v>0.68948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.768</v>
+        <v>0.76757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.752</v>
+        <v>0.73905</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.78481</v>
       </c>
       <c r="M4" t="n">
-        <v>0.698</v>
+        <v>0.69834</v>
       </c>
       <c r="N4" t="n">
-        <v>0.431</v>
+        <v>0.41286</v>
       </c>
       <c r="O4" t="n">
-        <v>0.318</v>
+        <v>0.28326</v>
       </c>
       <c r="P4" t="n">
-        <v>0.669</v>
+        <v>0.76112</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.113</v>
+        <v>0.10127</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06</v>
+        <v>0.05333</v>
       </c>
       <c r="T4" t="n">
-        <v>0.129</v>
+        <v>0.19807</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.5997</v>
       </c>
       <c r="V4" t="n">
-        <v>0.074</v>
+        <v>0.11863</v>
       </c>
       <c r="W4" t="n">
-        <v>0.498</v>
+        <v>0.49826</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.56667</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.445</v>
+        <v>0.4446</v>
       </c>
     </row>
     <row r="5">
@@ -2174,49 +2174,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.473</v>
+        <v>0.59636</v>
       </c>
       <c r="C5" t="n">
-        <v>0.516</v>
+        <v>0.58492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.60826</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.555</v>
+        <v>0.6869499999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.903</v>
+        <v>0.90837</v>
       </c>
       <c r="H5" t="n">
-        <v>0.706</v>
+        <v>0.65447</v>
       </c>
       <c r="I5" t="n">
-        <v>0.753</v>
+        <v>0.64512</v>
       </c>
       <c r="J5" t="n">
-        <v>0.664</v>
+        <v>0.66409</v>
       </c>
       <c r="K5" t="n">
-        <v>0.62</v>
+        <v>0.64497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.621</v>
+        <v>0.67247</v>
       </c>
       <c r="M5" t="n">
-        <v>0.62</v>
+        <v>0.6196199999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.39</v>
+        <v>0.427</v>
       </c>
       <c r="O5" t="n">
-        <v>0.282</v>
+        <v>0.30458</v>
       </c>
       <c r="P5" t="n">
-        <v>0.631</v>
+        <v>0.714</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2228,22 +2228,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.125</v>
+        <v>0.1916</v>
       </c>
       <c r="U5" t="n">
-        <v>0.472</v>
+        <v>0.56637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.1153</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0.50013</v>
       </c>
       <c r="X5" t="n">
-        <v>0.569</v>
+        <v>0.56897</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.446</v>
+        <v>0.44616</v>
       </c>
     </row>
   </sheetData>
@@ -2394,76 +2394,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.537</v>
+        <v>0.65396</v>
       </c>
       <c r="C2" t="n">
-        <v>0.524</v>
+        <v>0.59592</v>
       </c>
       <c r="D2" t="n">
-        <v>0.554</v>
+        <v>0.72705</v>
       </c>
       <c r="E2" t="n">
-        <v>0.714</v>
+        <v>0.82573</v>
       </c>
       <c r="F2" t="n">
-        <v>0.958</v>
+        <v>0.96334</v>
       </c>
       <c r="G2" t="n">
-        <v>0.57</v>
+        <v>0.72287</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.76659</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.93345</v>
       </c>
       <c r="J2" t="n">
-        <v>0.724</v>
+        <v>0.65159</v>
       </c>
       <c r="K2" t="n">
-        <v>0.752</v>
+        <v>0.81955</v>
       </c>
       <c r="L2" t="n">
-        <v>0.88</v>
+        <v>0.8798899999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.66</v>
+        <v>0.77235</v>
       </c>
       <c r="N2" t="n">
-        <v>0.376</v>
+        <v>0.40356</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.83095</v>
       </c>
       <c r="P2" t="n">
-        <v>0.245</v>
+        <v>0.26668</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.138</v>
+        <v>0.12443</v>
       </c>
       <c r="R2" t="n">
-        <v>0.078</v>
+        <v>0.06905</v>
       </c>
       <c r="S2" t="n">
-        <v>0.833</v>
+        <v>0.83333</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2</v>
+        <v>0.30096</v>
       </c>
       <c r="U2" t="n">
-        <v>0.145</v>
+        <v>0.2317</v>
       </c>
       <c r="V2" t="n">
-        <v>0.336</v>
+        <v>0.44672</v>
       </c>
       <c r="W2" t="n">
-        <v>0.526</v>
+        <v>0.52637</v>
       </c>
       <c r="X2" t="n">
-        <v>0.47</v>
+        <v>0.47017</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.615</v>
+        <v>0.61481</v>
       </c>
     </row>
     <row r="3">
@@ -2473,76 +2473,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.535</v>
+        <v>0.64733</v>
       </c>
       <c r="C3" t="n">
-        <v>0.518</v>
+        <v>0.59122</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.71852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.656</v>
+        <v>0.78955</v>
       </c>
       <c r="F3" t="n">
-        <v>0.958</v>
+        <v>0.9599299999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.499</v>
+        <v>0.67097</v>
       </c>
       <c r="H3" t="n">
-        <v>0.864</v>
+        <v>0.8106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.924</v>
+        <v>0.92395</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.72399</v>
       </c>
       <c r="K3" t="n">
-        <v>0.726</v>
+        <v>0.79108</v>
       </c>
       <c r="L3" t="n">
-        <v>0.871</v>
+        <v>0.87075</v>
       </c>
       <c r="M3" t="n">
-        <v>0.628</v>
+        <v>0.7309600000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.359</v>
+        <v>0.40594</v>
       </c>
       <c r="O3" t="n">
-        <v>0.776</v>
+        <v>0.78871</v>
       </c>
       <c r="P3" t="n">
-        <v>0.234</v>
+        <v>0.27356</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.116</v>
+        <v>0.10496</v>
       </c>
       <c r="R3" t="n">
-        <v>0.067</v>
+        <v>0.05968</v>
       </c>
       <c r="S3" t="n">
-        <v>0.667</v>
+        <v>0.66667</v>
       </c>
       <c r="T3" t="n">
-        <v>0.27</v>
+        <v>0.35381</v>
       </c>
       <c r="U3" t="n">
-        <v>0.216</v>
+        <v>0.28711</v>
       </c>
       <c r="V3" t="n">
-        <v>0.39</v>
+        <v>0.49177</v>
       </c>
       <c r="W3" t="n">
-        <v>0.529</v>
+        <v>0.52921</v>
       </c>
       <c r="X3" t="n">
-        <v>0.473</v>
+        <v>0.47291</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.617</v>
+        <v>0.61686</v>
       </c>
     </row>
     <row r="4">
@@ -2552,76 +2552,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.65193</v>
       </c>
       <c r="C4" t="n">
-        <v>0.595</v>
+        <v>0.60816</v>
       </c>
       <c r="D4" t="n">
-        <v>0.527</v>
+        <v>0.70399</v>
       </c>
       <c r="E4" t="n">
-        <v>0.759</v>
+        <v>0.8156</v>
       </c>
       <c r="F4" t="n">
-        <v>0.965</v>
+        <v>0.9674</v>
       </c>
       <c r="G4" t="n">
-        <v>0.625</v>
+        <v>0.70524</v>
       </c>
       <c r="H4" t="n">
-        <v>0.803</v>
+        <v>0.74871</v>
       </c>
       <c r="I4" t="n">
-        <v>0.82</v>
+        <v>0.81999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.788</v>
+        <v>0.68948</v>
       </c>
       <c r="K4" t="n">
-        <v>0.806</v>
+        <v>0.79018</v>
       </c>
       <c r="L4" t="n">
-        <v>0.79</v>
+        <v>0.79029</v>
       </c>
       <c r="M4" t="n">
-        <v>0.825</v>
+        <v>0.79349</v>
       </c>
       <c r="N4" t="n">
-        <v>0.485</v>
+        <v>0.45137</v>
       </c>
       <c r="O4" t="n">
-        <v>0.781</v>
+        <v>0.82447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.354</v>
+        <v>0.31103</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.177</v>
+        <v>0.15936</v>
       </c>
       <c r="R4" t="n">
-        <v>0.098</v>
+        <v>0.08711000000000001</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0.192</v>
+        <v>0.28677</v>
       </c>
       <c r="U4" t="n">
-        <v>0.123</v>
+        <v>0.19704</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.5997</v>
       </c>
       <c r="W4" t="n">
-        <v>0.513</v>
+        <v>0.51332</v>
       </c>
       <c r="X4" t="n">
-        <v>0.47</v>
+        <v>0.46976</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.56667</v>
       </c>
     </row>
     <row r="5">
@@ -2631,49 +2631,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.502</v>
+        <v>0.62552</v>
       </c>
       <c r="C5" t="n">
-        <v>0.525</v>
+        <v>0.59097</v>
       </c>
       <c r="D5" t="n">
-        <v>0.483</v>
+        <v>0.66603</v>
       </c>
       <c r="E5" t="n">
-        <v>0.702</v>
+        <v>0.8005100000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.958</v>
+        <v>0.9599299999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.555</v>
+        <v>0.6869499999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.722</v>
+        <v>0.66848</v>
       </c>
       <c r="I5" t="n">
-        <v>0.694</v>
+        <v>0.69391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.753</v>
+        <v>0.64512</v>
       </c>
       <c r="K5" t="n">
-        <v>0.669</v>
+        <v>0.69813</v>
       </c>
       <c r="L5" t="n">
-        <v>0.721</v>
+        <v>0.7212499999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.628</v>
+        <v>0.6805099999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.438</v>
+        <v>0.46086</v>
       </c>
       <c r="O5" t="n">
-        <v>0.75</v>
+        <v>0.78263</v>
       </c>
       <c r="P5" t="n">
-        <v>0.311</v>
+        <v>0.32699</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -2685,22 +2685,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.189</v>
+        <v>0.28096</v>
       </c>
       <c r="U5" t="n">
-        <v>0.122</v>
+        <v>0.19599</v>
       </c>
       <c r="V5" t="n">
-        <v>0.472</v>
+        <v>0.56637</v>
       </c>
       <c r="W5" t="n">
-        <v>0.516</v>
+        <v>0.51577</v>
       </c>
       <c r="X5" t="n">
-        <v>0.472</v>
+        <v>0.47219</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.569</v>
+        <v>0.56897</v>
       </c>
     </row>
   </sheetData>
